--- a/尝试查询表.xlsx
+++ b/尝试查询表.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\张天夫\Documents\MATLAB\Transfer-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F26F1A-7AD9-48E0-974B-49478B678FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48ED123-0EF6-434C-B044-0DFC7AE03676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CellReuse" sheetId="1" r:id="rId1"/>
-    <sheet name="CellReuse.V7" sheetId="3" r:id="rId2"/>
+    <sheet name="LT" sheetId="3" r:id="rId2"/>
     <sheet name="CellReuse.Cue" sheetId="4" r:id="rId3"/>
     <sheet name="CellReuse.RSPd" sheetId="6" r:id="rId4"/>
     <sheet name="LearnerMentor" sheetId="8" r:id="rId5"/>
+    <sheet name="MOpLT" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
   <si>
     <t>GroupName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,6 +124,18 @@
   </si>
   <si>
     <t>FinalLight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransferHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TransferMiss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Behavior</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -167,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -183,6 +195,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,7 +535,7 @@
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -528,7 +552,7 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -629,7 +653,7 @@
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -643,7 +667,7 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
@@ -658,7 +682,7 @@
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -675,7 +699,7 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
@@ -698,16 +722,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA14F78-2352-4996-93F4-423CE9EA31AB}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.625" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.625" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -717,11 +740,8 @@
       <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -731,11 +751,8 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,9 +761,6 @@
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -783,10 +797,10 @@
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -797,9 +811,9 @@
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -807,20 +821,20 @@
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -831,8 +845,8 @@
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
       <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
@@ -848,4 +862,84 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FDDBEF-D714-4F93-9194-8903239450AC}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.625" style="4" customWidth="1"/>
+    <col min="2" max="3" width="10.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>